--- a/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>354_桔叶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0555101051615100</v>
+        <v>0555101051615105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>864_黄洋金边红色_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0555101051615105</v>
+        <v>05551010516151051010202030302020150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05551010516151051010202030302020150</v>
+        <v>055510105161510510102020303020201520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,60 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +715,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>055510105161510510102020303020201520</v>
+        <v>055510105161510510102020303020201520101010101020</v>
       </c>
     </row>
   </sheetData>
